--- a/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Arm_AxRad.xlsx
+++ b/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Arm_AxRad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Subframe_Conn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B71B657-82E8-4EB7-AC3E-E07A5A11DD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4568D32A-D904-440B-B703-1513FBBC95FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="1920" windowWidth="21600" windowHeight="11295" tabRatio="988" activeTab="1" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
+    <workbookView xWindow="3375" yWindow="630" windowWidth="18825" windowHeight="11430" tabRatio="988" activeTab="1" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
   </bookViews>
   <sheets>
     <sheet name="Bushing_Sedan_UA" sheetId="4" r:id="rId1"/>

--- a/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Arm_AxRad.xlsx
+++ b/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Arm_AxRad.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Subframe_Conn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4568D32A-D904-440B-B703-1513FBBC95FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C21002-B5B9-414D-8F56-419C1072FB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="630" windowWidth="18825" windowHeight="11430" tabRatio="988" activeTab="1" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
+    <workbookView xWindow="29985" yWindow="990" windowWidth="28050" windowHeight="12510" tabRatio="988" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bushing_Sedan_UA" sheetId="4" r:id="rId1"/>
-    <sheet name="Bushing_Sedan_LA" sheetId="2" r:id="rId2"/>
+    <sheet name="Sef_DW_UA" sheetId="4" r:id="rId1"/>
+    <sheet name="Sef_DW_LA" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -132,10 +132,10 @@
     <t>Bushing_AxRad</t>
   </si>
   <si>
-    <t>BushArm_AxRad_Sedan_UA</t>
-  </si>
-  <si>
-    <t>BushArm_AxRad_Sedan_LA</t>
+    <t>BushArm_AxRad_Sef_DW_LA</t>
+  </si>
+  <si>
+    <t>BushArm_AxRad_Sef_DW_UA</t>
   </si>
 </sst>
 </file>
@@ -677,7 +677,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1380,7 +1380,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
